--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/GEORGIA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/GEORGIA_2017.xlsx
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C139">
@@ -3001,7 +3001,7 @@
         <v>25</v>
       </c>
       <c r="D147">
-        <v>0.0009713264433910949</v>
+        <v>0.0009713264433910948</v>
       </c>
     </row>
     <row r="148">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C189">
@@ -4567,7 +4567,7 @@
         <v>24</v>
       </c>
       <c r="D234">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="235">
@@ -5431,7 +5431,7 @@
         <v>24</v>
       </c>
       <c r="D282">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="283">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C327">
@@ -6637,7 +6637,7 @@
         <v>24</v>
       </c>
       <c r="D349">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="350">
@@ -8167,7 +8167,7 @@
         <v>24</v>
       </c>
       <c r="D434">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="435">
@@ -8635,7 +8635,7 @@
         <v>24</v>
       </c>
       <c r="D460">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="461">
@@ -8923,7 +8923,7 @@
         <v>25</v>
       </c>
       <c r="D476">
-        <v>0.0009713264433910949</v>
+        <v>0.0009713264433910948</v>
       </c>
     </row>
     <row r="477">
@@ -12127,7 +12127,7 @@
         <v>249</v>
       </c>
       <c r="D654">
-        <v>0.009674411376175305</v>
+        <v>0.009674411376175304</v>
       </c>
     </row>
     <row r="655">
@@ -12325,7 +12325,7 @@
         <v>25</v>
       </c>
       <c r="D665">
-        <v>0.0009713264433910949</v>
+        <v>0.0009713264433910948</v>
       </c>
     </row>
     <row r="666">
@@ -13711,7 +13711,7 @@
         <v>25</v>
       </c>
       <c r="D742">
-        <v>0.0009713264433910949</v>
+        <v>0.0009713264433910948</v>
       </c>
     </row>
     <row r="743">
@@ -13873,7 +13873,7 @@
         <v>25</v>
       </c>
       <c r="D751">
-        <v>0.0009713264433910949</v>
+        <v>0.0009713264433910948</v>
       </c>
     </row>
     <row r="752">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C761">
@@ -15259,7 +15259,7 @@
         <v>25</v>
       </c>
       <c r="D828">
-        <v>0.0009713264433910949</v>
+        <v>0.0009713264433910948</v>
       </c>
     </row>
     <row r="829">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C888">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C935">
@@ -17221,7 +17221,7 @@
         <v>24</v>
       </c>
       <c r="D937">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="938">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1022">
@@ -19399,7 +19399,7 @@
         <v>25</v>
       </c>
       <c r="D1058">
-        <v>0.0009713264433910949</v>
+        <v>0.0009713264433910948</v>
       </c>
     </row>
     <row r="1059">
@@ -21865,7 +21865,7 @@
         <v>24</v>
       </c>
       <c r="D1195">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="1196">
@@ -28057,7 +28057,7 @@
         <v>24</v>
       </c>
       <c r="D1539">
-        <v>0.0009324733856554511</v>
+        <v>0.0009324733856554512</v>
       </c>
     </row>
     <row r="1540">
